--- a/sample_input.xlsx
+++ b/sample_input.xlsx
@@ -12,7 +12,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7275"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -29,12 +29,6 @@
     <t>Compound</t>
   </si>
   <si>
-    <t>HOMO (eV)</t>
-  </si>
-  <si>
-    <t>LUMO (eV)</t>
-  </si>
-  <si>
     <t>D1</t>
   </si>
   <si>
@@ -45,6 +39,12 @@
   </si>
   <si>
     <t>D4</t>
+  </si>
+  <si>
+    <t>HOMO</t>
+  </si>
+  <si>
+    <t>LUMO</t>
   </si>
 </sst>
 </file>
@@ -383,28 +383,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15.28515625" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
       </c>
       <c r="B2" s="1">
         <v>-4.25</v>
@@ -412,11 +407,10 @@
       <c r="C2" s="1">
         <v>-2.25</v>
       </c>
-      <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1">
         <v>-4.7</v>
@@ -424,11 +418,10 @@
       <c r="C3" s="1">
         <v>-2.59</v>
       </c>
-      <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1">
         <v>-4.6900000000000004</v>
@@ -436,11 +429,10 @@
       <c r="C4" s="1">
         <v>-2.58</v>
       </c>
-      <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2">
         <v>-4.7699999999999996</v>
@@ -448,11 +440,9 @@
       <c r="C5" s="2">
         <v>-2.78</v>
       </c>
-      <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>